--- a/resources/bachelor_player_ratings_shared.xlsx
+++ b/resources/bachelor_player_ratings_shared.xlsx
@@ -689,7 +689,7 @@
           <t>Brad status</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>Set App Config!B2 to TRUE or FALSE. The app uses this as the shared scenario.</t>
         </is>
@@ -701,7 +701,7 @@
           <t>Before each game</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>Set Schedule &amp; Results status and Betting Locked?; use FINAL only after scores and box scores are checked.</t>
         </is>
@@ -713,7 +713,7 @@
           <t>Official scores</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>Enter team scores in Schedule &amp; Results, then mark Final? TRUE.</t>
         </is>
@@ -725,7 +725,7 @@
           <t>Official box scores</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>In Box Scores, use the active scenario rows, mark Played? TRUE, and enter PTS/REB/AST/3PM.</t>
         </is>
@@ -737,7 +737,7 @@
           <t>Bets</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>Do not hand-edit Bets or Bet Legs after Apps Script setup; the app appends ticket snapshots.</t>
         </is>
@@ -749,7 +749,7 @@
           <t>Leaderboards</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>Betting Leaderboard and Player Leaderboard derive from the raw Bets and Box Scores tabs.</t>
         </is>
@@ -761,7 +761,7 @@
           <t>Yellow cells</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>Organizer/scorekeeper inputs. Dark headers and calculated cells should not be edited.</t>
         </is>
@@ -1997,11 +1997,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
+      <c r="A2" s="0">
         <f>IFERROR(QUERY({Bets!C2:C,Bets!D2:D,Bets!J2:J,Bets!K2:K},"select Col1,count(Col1),sum(Col2),sum(Col3),sum(Col4) where Col1 is not null group by Col1 order by sum(Col4) desc label Col1 'Bettor',count(Col1) 'Tickets',sum(Col2) 'Total Staked',sum(Col3) 'Settled Return',sum(Col4) 'Profit'",0),"")</f>
         <v/>
       </c>
-      <c r="F2">
+      <c r="F2" s="0">
         <f>ARRAYFORMULA(IF(A2:A="","",100-C2:C+D2:D))</f>
         <v/>
       </c>
@@ -2068,7 +2068,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
+      <c r="A2" s="0">
         <f>IFERROR(QUERY('Box Scores'!A2:K,"select D,count(D),sum(G),sum(H),sum(I),sum(J),sum(K) where F = TRUE and B = '"&amp;IF('App Config'!B2,"Brad Plays","Brad Out")&amp;"' group by D order by sum(K) desc label D 'Player',count(D) 'Games',sum(G) 'Points',sum(H) 'Rebounds',sum(I) 'Assists',sum(J) 'Three Pointers',sum(K) 'PRA'",0),"")</f>
         <v/>
       </c>
@@ -2085,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" style="19" min="1" max="1"/>
@@ -2117,7 +2117,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>BRAD_PLAYS</t>
         </is>
@@ -2125,19 +2125,19 @@
       <c r="B2" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>FALSE uses Brad Out rosters; TRUE uses Brad Plays rosters.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>Organizer</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>BETTING_OPEN</t>
         </is>
@@ -2145,99 +2145,99 @@
       <c r="B3" s="23" t="b">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>Set FALSE to stop new centralized bets.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>Organizer</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>EVENT_ID</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>bachelor-basketball-2026</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>Stable identifier stored on every ticket.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>Leave unchanged</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>MODEL_VERSION</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>Increment after materially changing ratings or pricing assumptions.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>Organizer</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>STARTING_UNITS</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>Starting bankroll for each participant.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>Leave unchanged</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t>APPS_SCRIPT_URL</t>
         </is>
       </c>
       <c r="B7" s="23" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>Paste the deployed Google Apps Script /exec URL here.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>Organizer setup</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>AUTO_REFRESH_SECONDS</t>
         </is>
@@ -2245,12 +2245,78 @@
       <c r="B8" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>How often the app checks for shared results and leaderboard changes.</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>Organizer</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>TEAM_A_NAME</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>Team A</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Central display name used throughout the Sheet and website.</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>Organizer</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>TEAM_B_NAME</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>Team B</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Central display name used throughout the Sheet and website.</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>Organizer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t>TEAM_C_NAME</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Team C</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Central display name used throughout the Sheet and website.</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>Organizer</t>
         </is>
@@ -4615,2262 +4681,2262 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>Alex</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>Scoring</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="0" t="n">
         <v>6.846</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>Alex</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>Shooting</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>Alex</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>Playmaking / Handle</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="0" t="n">
         <v>6.308</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="0" t="n">
         <v>6.5</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="0" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>Alex</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>Defense</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>Alex</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>Rebounding / Size</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t>Alex</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>Stamina</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="0" t="n">
         <v>7.769</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="0" t="n">
         <v>-3</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>Peter</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>Scoring</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="0" t="n">
         <v>6.846</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
         <is>
           <t>Peter</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>Shooting</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr">
         <is>
           <t>Peter</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>Playmaking / Handle</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="0" t="n">
         <v>6.308</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="0" t="n">
         <v>8.5</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="0" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="0" t="inlineStr">
         <is>
           <t>Peter</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>Defense</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="0" t="inlineStr">
         <is>
           <t>Peter</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>Rebounding / Size</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="0" t="inlineStr">
         <is>
           <t>Peter</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>Stamina</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="0" t="n">
         <v>7.769</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="0" t="n">
         <v>-3</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="0" t="inlineStr">
         <is>
           <t>Andrew</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>Scoring</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="0" t="n">
         <v>6.846</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="0" t="inlineStr">
         <is>
           <t>Andrew</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>Shooting</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="0" t="inlineStr">
         <is>
           <t>Andrew</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>Playmaking / Handle</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="0" t="n">
         <v>6.308</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="0" t="n">
         <v>3.5</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="0" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="0" t="inlineStr">
         <is>
           <t>Andrew</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>Defense</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="0" t="inlineStr">
         <is>
           <t>Andrew</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>Rebounding / Size</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="0" t="inlineStr">
         <is>
           <t>Andrew</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>Stamina</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="0" t="n">
         <v>7.769</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="0" t="n">
         <v>-3</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
         <is>
           <t>Jason</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>Scoring</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="0" t="n">
         <v>6.846</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
         <is>
           <t>Jason</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>Shooting</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
         <is>
           <t>Jason</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>Playmaking / Handle</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="0" t="n">
         <v>6.308</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" s="0" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="0" t="inlineStr">
         <is>
           <t>Jason</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>Defense</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="0" t="inlineStr">
         <is>
           <t>Jason</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>Rebounding / Size</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="0" t="inlineStr">
         <is>
           <t>Jason</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>Stamina</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="0" t="n">
         <v>7.769</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" s="0" t="n">
         <v>-3</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="0" t="inlineStr">
         <is>
           <t>Eric</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>Scoring</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="0" t="n">
         <v>6.846</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="0" t="inlineStr">
         <is>
           <t>Eric</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>Shooting</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="0" t="inlineStr">
         <is>
           <t>Eric</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>Playmaking / Handle</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="0" t="n">
         <v>6.308</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" s="0" t="n">
         <v>6.5</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28" s="0" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="0" t="inlineStr">
         <is>
           <t>Eric</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>Defense</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="0" t="inlineStr">
         <is>
           <t>Eric</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="0" t="inlineStr">
         <is>
           <t>Rebounding / Size</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="0" t="inlineStr">
         <is>
           <t>Eric</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="0" t="inlineStr">
         <is>
           <t>Stamina</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="0" t="n">
         <v>7.769</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31" s="0" t="n">
         <v>-3</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="0" t="inlineStr">
         <is>
           <t>Josh</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="0" t="inlineStr">
         <is>
           <t>Scoring</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="0" t="n">
         <v>6.846</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="0" t="inlineStr">
         <is>
           <t>Josh</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="0" t="inlineStr">
         <is>
           <t>Shooting</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="0" t="inlineStr">
         <is>
           <t>Josh</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="0" t="inlineStr">
         <is>
           <t>Playmaking / Handle</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="C34" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="0" t="n">
         <v>6.308</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="0" t="n">
         <v>3.5</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34" s="0" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="0" t="inlineStr">
         <is>
           <t>Josh</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="0" t="inlineStr">
         <is>
           <t>Defense</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="0" t="inlineStr">
         <is>
           <t>Josh</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="0" t="inlineStr">
         <is>
           <t>Rebounding / Size</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="0" t="inlineStr">
         <is>
           <t>Josh</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="0" t="inlineStr">
         <is>
           <t>Stamina</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="0" t="n">
         <v>7.769</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37" s="0" t="n">
         <v>-3</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="0" t="inlineStr">
         <is>
           <t>Zak</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="0" t="inlineStr">
         <is>
           <t>Scoring</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="C38" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="0" t="n">
         <v>6.846</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="0" t="inlineStr">
         <is>
           <t>Zak</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="0" t="inlineStr">
         <is>
           <t>Shooting</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="C39" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="0" t="inlineStr">
         <is>
           <t>Zak</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="0" t="inlineStr">
         <is>
           <t>Playmaking / Handle</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="C40" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="0" t="n">
         <v>6.308</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="0" t="n">
         <v>6.5</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40" s="0" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="0" t="inlineStr">
         <is>
           <t>Zak</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="0" t="inlineStr">
         <is>
           <t>Defense</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="C41" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="0" t="inlineStr">
         <is>
           <t>Zak</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="0" t="inlineStr">
         <is>
           <t>Rebounding / Size</t>
         </is>
       </c>
-      <c r="C42" t="n">
+      <c r="C42" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="0" t="inlineStr">
         <is>
           <t>Zak</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="0" t="inlineStr">
         <is>
           <t>Stamina</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="C43" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="0" t="n">
         <v>7.769</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43" s="0" t="n">
         <v>-3</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="0" t="inlineStr">
         <is>
           <t>James</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="0" t="inlineStr">
         <is>
           <t>Scoring</t>
         </is>
       </c>
-      <c r="C44" t="n">
+      <c r="C44" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="0" t="n">
         <v>6.846</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="0" t="inlineStr">
         <is>
           <t>James</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="0" t="inlineStr">
         <is>
           <t>Shooting</t>
         </is>
       </c>
-      <c r="C45" t="n">
+      <c r="C45" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="0" t="inlineStr">
         <is>
           <t>James</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="0" t="inlineStr">
         <is>
           <t>Playmaking / Handle</t>
         </is>
       </c>
-      <c r="C46" t="n">
+      <c r="C46" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="0" t="n">
         <v>6.308</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F46" s="0" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="0" t="inlineStr">
         <is>
           <t>James</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="0" t="inlineStr">
         <is>
           <t>Defense</t>
         </is>
       </c>
-      <c r="C47" t="n">
+      <c r="C47" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="0" t="inlineStr">
         <is>
           <t>James</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="0" t="inlineStr">
         <is>
           <t>Rebounding / Size</t>
         </is>
       </c>
-      <c r="C48" t="n">
+      <c r="C48" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F48" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="0" t="inlineStr">
         <is>
           <t>James</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="0" t="inlineStr">
         <is>
           <t>Stamina</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="C49" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="0" t="n">
         <v>7.769</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F49" s="0" t="n">
         <v>-3</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="0" t="inlineStr">
         <is>
           <t>Emil</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="0" t="inlineStr">
         <is>
           <t>Scoring</t>
         </is>
       </c>
-      <c r="C50" t="n">
+      <c r="C50" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="0" t="n">
         <v>6.846</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F50" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="0" t="inlineStr">
         <is>
           <t>Emil</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="0" t="inlineStr">
         <is>
           <t>Shooting</t>
         </is>
       </c>
-      <c r="C51" t="n">
+      <c r="C51" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F51" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="0" t="inlineStr">
         <is>
           <t>Emil</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="0" t="inlineStr">
         <is>
           <t>Playmaking / Handle</t>
         </is>
       </c>
-      <c r="C52" t="n">
+      <c r="C52" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="0" t="n">
         <v>6.308</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52" s="0" t="n">
         <v>5.5</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F52" s="0" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="0" t="inlineStr">
         <is>
           <t>Emil</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="0" t="inlineStr">
         <is>
           <t>Defense</t>
         </is>
       </c>
-      <c r="C53" t="n">
+      <c r="C53" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F53" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="0" t="inlineStr">
         <is>
           <t>Emil</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="0" t="inlineStr">
         <is>
           <t>Rebounding / Size</t>
         </is>
       </c>
-      <c r="C54" t="n">
+      <c r="C54" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F54" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G54" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="0" t="inlineStr">
         <is>
           <t>Emil</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="0" t="inlineStr">
         <is>
           <t>Stamina</t>
         </is>
       </c>
-      <c r="C55" t="n">
+      <c r="C55" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="0" t="n">
         <v>7.769</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F55" s="0" t="n">
         <v>-3</v>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G55" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="0" t="inlineStr">
         <is>
           <t>Darryl</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="0" t="inlineStr">
         <is>
           <t>Scoring</t>
         </is>
       </c>
-      <c r="C56" t="n">
+      <c r="C56" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="0" t="n">
         <v>6.846</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F56" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G56" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="0" t="inlineStr">
         <is>
           <t>Darryl</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="0" t="inlineStr">
         <is>
           <t>Shooting</t>
         </is>
       </c>
-      <c r="C57" t="n">
+      <c r="C57" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F57" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G57" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="0" t="inlineStr">
         <is>
           <t>Darryl</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="0" t="inlineStr">
         <is>
           <t>Playmaking / Handle</t>
         </is>
       </c>
-      <c r="C58" t="n">
+      <c r="C58" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="0" t="n">
         <v>6.308</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58" s="0" t="n">
         <v>4.5</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58" s="0" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G58" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="0" t="inlineStr">
         <is>
           <t>Darryl</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="0" t="inlineStr">
         <is>
           <t>Defense</t>
         </is>
       </c>
-      <c r="C59" t="n">
+      <c r="C59" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G59" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="0" t="inlineStr">
         <is>
           <t>Darryl</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="0" t="inlineStr">
         <is>
           <t>Rebounding / Size</t>
         </is>
       </c>
-      <c r="C60" t="n">
+      <c r="C60" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F60" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G60" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="0" t="inlineStr">
         <is>
           <t>Darryl</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="0" t="inlineStr">
         <is>
           <t>Stamina</t>
         </is>
       </c>
-      <c r="C61" t="n">
+      <c r="C61" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="0" t="n">
         <v>7.769</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="F61" t="n">
+      <c r="F61" s="0" t="n">
         <v>-3</v>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G61" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="0" t="inlineStr">
         <is>
           <t>Berler</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="0" t="inlineStr">
         <is>
           <t>Scoring</t>
         </is>
       </c>
-      <c r="C62" t="n">
+      <c r="C62" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="0" t="n">
         <v>6.846</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F62" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G62" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="0" t="inlineStr">
         <is>
           <t>Berler</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="0" t="inlineStr">
         <is>
           <t>Shooting</t>
         </is>
       </c>
-      <c r="C63" t="n">
+      <c r="C63" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F63" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G63" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="0" t="inlineStr">
         <is>
           <t>Berler</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="0" t="inlineStr">
         <is>
           <t>Playmaking / Handle</t>
         </is>
       </c>
-      <c r="C64" t="n">
+      <c r="C64" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="0" t="n">
         <v>6.308</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E64" s="0" t="n">
         <v>3.5</v>
       </c>
-      <c r="F64" t="n">
+      <c r="F64" s="0" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G64" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="0" t="inlineStr">
         <is>
           <t>Berler</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="0" t="inlineStr">
         <is>
           <t>Defense</t>
         </is>
       </c>
-      <c r="C65" t="n">
+      <c r="C65" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E65" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="F65" t="n">
+      <c r="F65" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G65" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="0" t="inlineStr">
         <is>
           <t>Berler</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="0" t="inlineStr">
         <is>
           <t>Rebounding / Size</t>
         </is>
       </c>
-      <c r="C66" t="n">
+      <c r="C66" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E66" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="F66" t="n">
+      <c r="F66" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G66" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="0" t="inlineStr">
         <is>
           <t>Berler</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="0" t="inlineStr">
         <is>
           <t>Stamina</t>
         </is>
       </c>
-      <c r="C67" t="n">
+      <c r="C67" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="0" t="n">
         <v>7.769</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="F67" t="n">
+      <c r="F67" s="0" t="n">
         <v>-3</v>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G67" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="0" t="inlineStr">
         <is>
           <t>Alan</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="0" t="inlineStr">
         <is>
           <t>Scoring</t>
         </is>
       </c>
-      <c r="C68" t="n">
+      <c r="C68" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="0" t="n">
         <v>6.846</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E68" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="F68" t="n">
+      <c r="F68" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G68" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="0" t="inlineStr">
         <is>
           <t>Alan</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="0" t="inlineStr">
         <is>
           <t>Shooting</t>
         </is>
       </c>
-      <c r="C69" t="n">
+      <c r="C69" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F69" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G69" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="0" t="inlineStr">
         <is>
           <t>Alan</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="0" t="inlineStr">
         <is>
           <t>Playmaking / Handle</t>
         </is>
       </c>
-      <c r="C70" t="n">
+      <c r="C70" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="0" t="n">
         <v>6.308</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E70" s="0" t="n">
         <v>4.5</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F70" s="0" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G70" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="0" t="inlineStr">
         <is>
           <t>Alan</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="0" t="inlineStr">
         <is>
           <t>Defense</t>
         </is>
       </c>
-      <c r="C71" t="n">
+      <c r="C71" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="F71" t="n">
+      <c r="F71" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G71" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="0" t="inlineStr">
         <is>
           <t>Alan</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="0" t="inlineStr">
         <is>
           <t>Rebounding / Size</t>
         </is>
       </c>
-      <c r="C72" t="n">
+      <c r="C72" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E72" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F72" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G72" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="0" t="inlineStr">
         <is>
           <t>Alan</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="0" t="inlineStr">
         <is>
           <t>Stamina</t>
         </is>
       </c>
-      <c r="C73" t="n">
+      <c r="C73" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="0" t="n">
         <v>7.769</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E73" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="F73" t="n">
+      <c r="F73" s="0" t="n">
         <v>-3</v>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G73" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="0" t="inlineStr">
         <is>
           <t>Brad</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="0" t="inlineStr">
         <is>
           <t>Scoring</t>
         </is>
       </c>
-      <c r="C74" t="n">
+      <c r="C74" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="0" t="n">
         <v>6.846</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E74" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F74" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G74" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="0" t="inlineStr">
         <is>
           <t>Brad</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="0" t="inlineStr">
         <is>
           <t>Shooting</t>
         </is>
       </c>
-      <c r="C75" t="n">
+      <c r="C75" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F75" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G75" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="0" t="inlineStr">
         <is>
           <t>Brad</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="0" t="inlineStr">
         <is>
           <t>Playmaking / Handle</t>
         </is>
       </c>
-      <c r="C76" t="n">
+      <c r="C76" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="0" t="n">
         <v>6.308</v>
       </c>
-      <c r="E76" t="n">
+      <c r="E76" s="0" t="n">
         <v>6.5</v>
       </c>
-      <c r="F76" t="n">
+      <c r="F76" s="0" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G76" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="0" t="inlineStr">
         <is>
           <t>Brad</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="0" t="inlineStr">
         <is>
           <t>Defense</t>
         </is>
       </c>
-      <c r="C77" t="n">
+      <c r="C77" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E77" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F77" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G77" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="0" t="inlineStr">
         <is>
           <t>Brad</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="0" t="inlineStr">
         <is>
           <t>Rebounding / Size</t>
         </is>
       </c>
-      <c r="C78" t="n">
+      <c r="C78" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" s="0" t="n">
         <v>6.923</v>
       </c>
-      <c r="E78" t="n">
+      <c r="E78" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="F78" t="n">
+      <c r="F78" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G78" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="0" t="inlineStr">
         <is>
           <t>Brad</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="0" t="inlineStr">
         <is>
           <t>Stamina</t>
         </is>
       </c>
-      <c r="C79" t="n">
+      <c r="C79" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" s="0" t="n">
         <v>7.769</v>
       </c>
-      <c r="E79" t="n">
+      <c r="E79" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="F79" t="n">
+      <c r="F79" s="0" t="n">
         <v>-3</v>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G79" s="0" t="inlineStr">
         <is>
           <t>Original relative gaps preserved; category mean shifted to 5 and rounded to 0.5.</t>
         </is>
@@ -9941,25 +10007,25 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>game-1</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>Team A</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>Team B</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
           <t>Team C</t>
         </is>
@@ -9992,25 +10058,25 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>game-2</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>Team B</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>Team C</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>Team A</t>
         </is>
@@ -10043,25 +10109,25 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>game-3</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>Team C</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>Team A</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>Team B</t>
         </is>
@@ -10193,27 +10259,27 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>game-1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>Brad Out</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>alex</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>Alex</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
           <t>Team A</t>
         </is>
@@ -10225,34 +10291,34 @@
       <c r="H2" s="23" t="inlineStr"/>
       <c r="I2" s="23" t="inlineStr"/>
       <c r="J2" s="23" t="inlineStr"/>
-      <c r="K2">
+      <c r="K2" s="0">
         <f>IF(F2,SUM(G2:I2),"")</f>
         <v/>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>game-1</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>Brad Out</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>peter</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>Peter</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>Team A</t>
         </is>
@@ -10264,34 +10330,34 @@
       <c r="H3" s="23" t="inlineStr"/>
       <c r="I3" s="23" t="inlineStr"/>
       <c r="J3" s="23" t="inlineStr"/>
-      <c r="K3">
+      <c r="K3" s="0">
         <f>IF(F3,SUM(G3:I3),"")</f>
         <v/>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>game-1</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>Brad Out</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>andrew</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>Andrew</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>Team A</t>
         </is>
@@ -10303,34 +10369,34 @@
       <c r="H4" s="23" t="inlineStr"/>
       <c r="I4" s="23" t="inlineStr"/>
       <c r="J4" s="23" t="inlineStr"/>
-      <c r="K4">
+      <c r="K4" s="0">
         <f>IF(F4,SUM(G4:I4),"")</f>
         <v/>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>game-1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>Brad Out</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>jason</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>Jason</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>Team A</t>
         </is>
@@ -10342,34 +10408,34 @@
       <c r="H5" s="23" t="inlineStr"/>
       <c r="I5" s="23" t="inlineStr"/>
       <c r="J5" s="23" t="inlineStr"/>
-      <c r="K5">
+      <c r="K5" s="0">
         <f>IF(F5,SUM(G5:I5),"")</f>
         <v/>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>game-1</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>Brad Out</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>eric</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>Eric</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>Team B</t>
         </is>
@@ -10381,34 +10447,34 @@
       <c r="H6" s="23" t="inlineStr"/>
       <c r="I6" s="23" t="inlineStr"/>
       <c r="J6" s="23" t="inlineStr"/>
-      <c r="K6">
+      <c r="K6" s="0">
         <f>IF(F6,SUM(G6:I6),"")</f>
         <v/>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t>game-1</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>Brad Out</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>josh</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>Josh</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>Team B</t>
         </is>
@@ -10420,34 +10486,34 @@
       <c r="H7" s="23" t="inlineStr"/>
       <c r="I7" s="23" t="inlineStr"/>
       <c r="J7" s="23" t="inlineStr"/>
-      <c r="K7">
+      <c r="K7" s="0">
         <f>IF(F7,SUM(G7:I7),"")</f>
         <v/>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>game-1</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>Brad Out</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>zak</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>Zak</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>Team B</t>
         </is>
@@ -10459,34 +10525,34 @@
       <c r="H8" s="23" t="inlineStr"/>
       <c r="I8" s="23" t="inlineStr"/>
       <c r="J8" s="23" t="inlineStr"/>
-      <c r="K8">
+      <c r="K8" s="0">
         <f>IF(F8,SUM(G8:I8),"")</f>
         <v/>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
         <is>
           <t>game-1</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>Brad Out</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>james</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>James</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="0" t="inlineStr">
         <is>
           <t>Team B</t>
         </is>
@@ -10498,34 +10564,34 @@
       <c r="H9" s="23" t="inlineStr"/>
       <c r="I9" s="23" t="inlineStr"/>
       <c r="J9" s="23" t="inlineStr"/>
-      <c r="K9">
+      <c r="K9" s="0">
         <f>IF(F9,SUM(G9:I9),"")</f>
         <v/>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr">
         <is>
           <t>game-2</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>Brad Out</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>eric</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <is>
           <t>Eric</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>Team B</t>
         </is>
@@ -10537,34 +10603,34 @@
       <c r="H10" s="23" t="inlineStr"/>
       <c r="I10" s="23" t="inlineStr"/>
       <c r="J10" s="23" t="inlineStr"/>
-      <c r="K10">
+      <c r="K10" s="0">
         <f>IF(F10,SUM(G10:I10),"")</f>
         <v/>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="0" t="inlineStr">
         <is>
           <t>game-2</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>Brad Out</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>josh</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>Josh</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="0" t="inlineStr">
         <is>
           <t>Team B</t>
         </is>
@@ -10576,34 +10642,34 @@
       <c r="H11" s="23" t="inlineStr"/>
       <c r="I11" s="23" t="inlineStr"/>
       <c r="J11" s="23" t="inlineStr"/>
-      <c r="K11">
+      <c r="K11" s="0">
         <f>IF(F11,SUM(G11:I11),"")</f>
         <v/>
       </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="0" t="inlineStr">
         <is>
           <t>game-2</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>Brad Out</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>zak</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>Zak</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>Team B</t>
         </is>
@@ -10615,34 +10681,34 @@
       <c r="H12" s="23" t="inlineStr"/>
       <c r="I12" s="23" t="inlineStr"/>
       <c r="J12" s="23" t="inlineStr"/>
-      <c r="K12">
+      <c r="K12" s="0">
         <f>IF(F12,SUM(G12:I12),"")</f>
         <v/>
       </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="0" t="inlineStr">
         <is>
           <t>game-2</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>Brad Out</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>james</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>James</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>Team B</t>
         </is>
@@ -10654,34 +10720,34 @@
       <c r="H13" s="23" t="inlineStr"/>
       <c r="I13" s="23" t="inlineStr"/>
       <c r="J13" s="23" t="inlineStr"/>
-      <c r="K13">
+      <c r="K13" s="0">
         <f>IF(F13,SUM(G13:I13),"")</f>
         <v/>
       </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="0" t="inlineStr">
         <is>
           <t>game-2</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>Brad Out</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>emil</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t>Emil</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="0" t="inlineStr">
         <is>
           <t>Team C</t>
         </is>
@@ -10693,34 +10759,34 @@
       <c r="H14" s="23" t="inlineStr"/>
       <c r="I14" s="23" t="inlineStr"/>
       <c r="J14" s="23" t="inlineStr"/>
-      <c r="K14">
+      <c r="K14" s="0">
         <f>IF(F14,SUM(G14:I14),"")</f>
         <v/>
       </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="0" t="inlineStr">
         <is>
           <t>game-2</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>Brad Out</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="0" t="inlineStr">
         <is>
           <t>darryl</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="0" t="inlineStr">
         <is>
           <t>Darryl</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="0" t="inlineStr">
         <is>
           <t>Team C</t>
         </is>
@@ -10732,34 +10798,34 @@
       <c r="H15" s="23" t="inlineStr"/>
       <c r="I15" s="23" t="inlineStr"/>
       <c r="J15" s="23" t="inlineStr"/>
-      <c r="K15">
+      <c r="K15" s="0">
         <f>IF(F15,SUM(G15:I15),"")</f>
         <v/>
       </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="0" t="inlineStr">
         <is>
           <t>game-2</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>Brad Out</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="0" t="inlineStr">
         <is>
           <t>berler</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="0" t="inlineStr">
         <is>
           <t>Berler</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="0" t="inlineStr">
         <is>
           <t>Team C</t>
         </is>
@@ -10771,34 +10837,34 @@
       <c r="H16" s="23" t="inlineStr"/>
       <c r="I16" s="23" t="inlineStr"/>
       <c r="J16" s="23" t="inlineStr"/>
-      <c r="K16">
+      <c r="K16" s="0">
         <f>IF(F16,SUM(G16:I16),"")</f>
         <v/>
       </c>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="0" t="inlineStr">
         <is>
           <t>game-2</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>Brad Out</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="0" t="inlineStr">
         <is>
           <t>alan</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="0" t="inlineStr">
         <is>
           <t>Alan</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="0" t="inlineStr">
         <is>
           <t>Team C</t>
         </is>
@@ -10810,34 +10876,34 @@
       <c r="H17" s="23" t="inlineStr"/>
       <c r="I17" s="23" t="inlineStr"/>
       <c r="J17" s="23" t="inlineStr"/>
-      <c r="K17">
+      <c r="K17" s="0">
         <f>IF(F17,SUM(G17:I17),"")</f>
         <v/>
       </c>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="0" t="inlineStr">
         <is>
           <t>game-3</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>Brad Out</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="0" t="inlineStr">
         <is>
           <t>alex</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="0" t="inlineStr">
         <is>
           <t>Alex</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="0" t="inlineStr">
         <is>
           <t>Team A</t>
         </is>
@@ -10849,34 +10915,34 @@
       <c r="H18" s="23" t="inlineStr"/>
       <c r="I18" s="23" t="inlineStr"/>
       <c r="J18" s="23" t="inlineStr"/>
-      <c r="K18">
+      <c r="K18" s="0">
         <f>IF(F18,SUM(G18:I18),"")</f>
         <v/>
       </c>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="0" t="inlineStr">
         <is>
           <t>game-3</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>Brad Out</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="0" t="inlineStr">
         <is>
           <t>peter</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="0" t="inlineStr">
         <is>
           <t>Peter</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="0" t="inlineStr">
         <is>
           <t>Team A</t>
         </is>
@@ -10888,34 +10954,34 @@
       <c r="H19" s="23" t="inlineStr"/>
       <c r="I19" s="23" t="inlineStr"/>
       <c r="J19" s="23" t="inlineStr"/>
-      <c r="K19">
+      <c r="K19" s="0">
         <f>IF(F19,SUM(G19:I19),"")</f>
         <v/>
       </c>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
         <is>
           <t>game-3</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>Brad Out</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="0" t="inlineStr">
         <is>
           <t>andrew</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="0" t="inlineStr">
         <is>
           <t>Andrew</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="0" t="inlineStr">
         <is>
           <t>Team A</t>
         </is>
@@ -10927,34 +10993,34 @@
       <c r="H20" s="23" t="inlineStr"/>
       <c r="I20" s="23" t="inlineStr"/>
       <c r="J20" s="23" t="inlineStr"/>
-      <c r="K20">
+      <c r="K20" s="0">
         <f>IF(F20,SUM(G20:I20),"")</f>
         <v/>
       </c>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" s="0" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
         <is>
           <t>game-3</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>Brad Out</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="0" t="inlineStr">
         <is>
           <t>jason</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="0" t="inlineStr">
         <is>
           <t>Jason</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="0" t="inlineStr">
         <is>
           <t>Team A</t>
         </is>
@@ -10966,34 +11032,34 @@
       <c r="H21" s="23" t="inlineStr"/>
       <c r="I21" s="23" t="inlineStr"/>
       <c r="J21" s="23" t="inlineStr"/>
-      <c r="K21">
+      <c r="K21" s="0">
         <f>IF(F21,SUM(G21:I21),"")</f>
         <v/>
       </c>
-      <c r="L21" t="inlineStr"/>
+      <c r="L21" s="0" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
         <is>
           <t>game-3</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>Brad Out</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
         <is>
           <t>emil</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="0" t="inlineStr">
         <is>
           <t>Emil</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="0" t="inlineStr">
         <is>
           <t>Team C</t>
         </is>
@@ -11005,34 +11071,34 @@
       <c r="H22" s="23" t="inlineStr"/>
       <c r="I22" s="23" t="inlineStr"/>
       <c r="J22" s="23" t="inlineStr"/>
-      <c r="K22">
+      <c r="K22" s="0">
         <f>IF(F22,SUM(G22:I22),"")</f>
         <v/>
       </c>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" s="0" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="0" t="inlineStr">
         <is>
           <t>game-3</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>Brad Out</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr">
         <is>
           <t>darryl</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="0" t="inlineStr">
         <is>
           <t>Darryl</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="0" t="inlineStr">
         <is>
           <t>Team C</t>
         </is>
@@ -11044,34 +11110,34 @@
       <c r="H23" s="23" t="inlineStr"/>
       <c r="I23" s="23" t="inlineStr"/>
       <c r="J23" s="23" t="inlineStr"/>
-      <c r="K23">
+      <c r="K23" s="0">
         <f>IF(F23,SUM(G23:I23),"")</f>
         <v/>
       </c>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" s="0" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="0" t="inlineStr">
         <is>
           <t>game-3</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>Brad Out</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
         <is>
           <t>berler</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="0" t="inlineStr">
         <is>
           <t>Berler</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="0" t="inlineStr">
         <is>
           <t>Team C</t>
         </is>
@@ -11083,34 +11149,34 @@
       <c r="H24" s="23" t="inlineStr"/>
       <c r="I24" s="23" t="inlineStr"/>
       <c r="J24" s="23" t="inlineStr"/>
-      <c r="K24">
+      <c r="K24" s="0">
         <f>IF(F24,SUM(G24:I24),"")</f>
         <v/>
       </c>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" s="0" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="0" t="inlineStr">
         <is>
           <t>game-3</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>Brad Out</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr">
         <is>
           <t>alan</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="0" t="inlineStr">
         <is>
           <t>Alan</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="0" t="inlineStr">
         <is>
           <t>Team C</t>
         </is>
@@ -11122,34 +11188,34 @@
       <c r="H25" s="23" t="inlineStr"/>
       <c r="I25" s="23" t="inlineStr"/>
       <c r="J25" s="23" t="inlineStr"/>
-      <c r="K25">
+      <c r="K25" s="0">
         <f>IF(F25,SUM(G25:I25),"")</f>
         <v/>
       </c>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" s="0" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="0" t="inlineStr">
         <is>
           <t>game-1</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>Brad Plays</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="0" t="inlineStr">
         <is>
           <t>alex</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="0" t="inlineStr">
         <is>
           <t>Alex</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="0" t="inlineStr">
         <is>
           <t>Team A</t>
         </is>
@@ -11161,34 +11227,34 @@
       <c r="H26" s="23" t="inlineStr"/>
       <c r="I26" s="23" t="inlineStr"/>
       <c r="J26" s="23" t="inlineStr"/>
-      <c r="K26">
+      <c r="K26" s="0">
         <f>IF(F26,SUM(G26:I26),"")</f>
         <v/>
       </c>
-      <c r="L26" t="inlineStr"/>
+      <c r="L26" s="0" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="0" t="inlineStr">
         <is>
           <t>game-1</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>Brad Plays</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="0" t="inlineStr">
         <is>
           <t>peter</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="0" t="inlineStr">
         <is>
           <t>Peter</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="0" t="inlineStr">
         <is>
           <t>Team A</t>
         </is>
@@ -11200,34 +11266,34 @@
       <c r="H27" s="23" t="inlineStr"/>
       <c r="I27" s="23" t="inlineStr"/>
       <c r="J27" s="23" t="inlineStr"/>
-      <c r="K27">
+      <c r="K27" s="0">
         <f>IF(F27,SUM(G27:I27),"")</f>
         <v/>
       </c>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" s="0" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="0" t="inlineStr">
         <is>
           <t>game-1</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>Brad Plays</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="0" t="inlineStr">
         <is>
           <t>josh</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="0" t="inlineStr">
         <is>
           <t>Josh</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="0" t="inlineStr">
         <is>
           <t>Team A</t>
         </is>
@@ -11239,34 +11305,34 @@
       <c r="H28" s="23" t="inlineStr"/>
       <c r="I28" s="23" t="inlineStr"/>
       <c r="J28" s="23" t="inlineStr"/>
-      <c r="K28">
+      <c r="K28" s="0">
         <f>IF(F28,SUM(G28:I28),"")</f>
         <v/>
       </c>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" s="0" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="0" t="inlineStr">
         <is>
           <t>game-1</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>Brad Plays</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="0" t="inlineStr">
         <is>
           <t>berler</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="0" t="inlineStr">
         <is>
           <t>Berler</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="0" t="inlineStr">
         <is>
           <t>Team A</t>
         </is>
@@ -11278,38 +11344,38 @@
       <c r="H29" s="23" t="inlineStr"/>
       <c r="I29" s="23" t="inlineStr"/>
       <c r="J29" s="23" t="inlineStr"/>
-      <c r="K29">
+      <c r="K29" s="0">
         <f>IF(F29,SUM(G29:I29),"")</f>
         <v/>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L29" s="0" t="inlineStr">
         <is>
           <t>Shared sub slot</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="0" t="inlineStr">
         <is>
           <t>game-1</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="0" t="inlineStr">
         <is>
           <t>Brad Plays</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="0" t="inlineStr">
         <is>
           <t>jason</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="0" t="inlineStr">
         <is>
           <t>Jason</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="0" t="inlineStr">
         <is>
           <t>Team A</t>
         </is>
@@ -11321,38 +11387,38 @@
       <c r="H30" s="23" t="inlineStr"/>
       <c r="I30" s="23" t="inlineStr"/>
       <c r="J30" s="23" t="inlineStr"/>
-      <c r="K30">
+      <c r="K30" s="0">
         <f>IF(F30,SUM(G30:I30),"")</f>
         <v/>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L30" s="0" t="inlineStr">
         <is>
           <t>Shared sub slot</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="0" t="inlineStr">
         <is>
           <t>game-1</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="0" t="inlineStr">
         <is>
           <t>Brad Plays</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="0" t="inlineStr">
         <is>
           <t>eric</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="0" t="inlineStr">
         <is>
           <t>Eric</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="0" t="inlineStr">
         <is>
           <t>Team B</t>
         </is>
@@ -11364,34 +11430,34 @@
       <c r="H31" s="23" t="inlineStr"/>
       <c r="I31" s="23" t="inlineStr"/>
       <c r="J31" s="23" t="inlineStr"/>
-      <c r="K31">
+      <c r="K31" s="0">
         <f>IF(F31,SUM(G31:I31),"")</f>
         <v/>
       </c>
-      <c r="L31" t="inlineStr"/>
+      <c r="L31" s="0" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="0" t="inlineStr">
         <is>
           <t>game-1</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="0" t="inlineStr">
         <is>
           <t>Brad Plays</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="0" t="inlineStr">
         <is>
           <t>zak</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="0" t="inlineStr">
         <is>
           <t>Zak</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="0" t="inlineStr">
         <is>
           <t>Team B</t>
         </is>
@@ -11403,34 +11469,34 @@
       <c r="H32" s="23" t="inlineStr"/>
       <c r="I32" s="23" t="inlineStr"/>
       <c r="J32" s="23" t="inlineStr"/>
-      <c r="K32">
+      <c r="K32" s="0">
         <f>IF(F32,SUM(G32:I32),"")</f>
         <v/>
       </c>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" s="0" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="0" t="inlineStr">
         <is>
           <t>game-1</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="0" t="inlineStr">
         <is>
           <t>Brad Plays</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="0" t="inlineStr">
         <is>
           <t>brad</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="0" t="inlineStr">
         <is>
           <t>Brad</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="0" t="inlineStr">
         <is>
           <t>Team B</t>
         </is>
@@ -11442,34 +11508,34 @@
       <c r="H33" s="23" t="inlineStr"/>
       <c r="I33" s="23" t="inlineStr"/>
       <c r="J33" s="23" t="inlineStr"/>
-      <c r="K33">
+      <c r="K33" s="0">
         <f>IF(F33,SUM(G33:I33),"")</f>
         <v/>
       </c>
-      <c r="L33" t="inlineStr"/>
+      <c r="L33" s="0" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="0" t="inlineStr">
         <is>
           <t>game-1</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="0" t="inlineStr">
         <is>
           <t>Brad Plays</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="0" t="inlineStr">
         <is>
           <t>james</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="0" t="inlineStr">
         <is>
           <t>James</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="0" t="inlineStr">
         <is>
           <t>Team B</t>
         </is>
@@ -11481,34 +11547,34 @@
       <c r="H34" s="23" t="inlineStr"/>
       <c r="I34" s="23" t="inlineStr"/>
       <c r="J34" s="23" t="inlineStr"/>
-      <c r="K34">
+      <c r="K34" s="0">
         <f>IF(F34,SUM(G34:I34),"")</f>
         <v/>
       </c>
-      <c r="L34" t="inlineStr"/>
+      <c r="L34" s="0" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="0" t="inlineStr">
         <is>
           <t>game-2</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="0" t="inlineStr">
         <is>
           <t>Brad Plays</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="0" t="inlineStr">
         <is>
           <t>eric</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="0" t="inlineStr">
         <is>
           <t>Eric</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="0" t="inlineStr">
         <is>
           <t>Team B</t>
         </is>
@@ -11520,34 +11586,34 @@
       <c r="H35" s="23" t="inlineStr"/>
       <c r="I35" s="23" t="inlineStr"/>
       <c r="J35" s="23" t="inlineStr"/>
-      <c r="K35">
+      <c r="K35" s="0">
         <f>IF(F35,SUM(G35:I35),"")</f>
         <v/>
       </c>
-      <c r="L35" t="inlineStr"/>
+      <c r="L35" s="0" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="0" t="inlineStr">
         <is>
           <t>game-2</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="0" t="inlineStr">
         <is>
           <t>Brad Plays</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="0" t="inlineStr">
         <is>
           <t>zak</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="0" t="inlineStr">
         <is>
           <t>Zak</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="0" t="inlineStr">
         <is>
           <t>Team B</t>
         </is>
@@ -11559,34 +11625,34 @@
       <c r="H36" s="23" t="inlineStr"/>
       <c r="I36" s="23" t="inlineStr"/>
       <c r="J36" s="23" t="inlineStr"/>
-      <c r="K36">
+      <c r="K36" s="0">
         <f>IF(F36,SUM(G36:I36),"")</f>
         <v/>
       </c>
-      <c r="L36" t="inlineStr"/>
+      <c r="L36" s="0" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="0" t="inlineStr">
         <is>
           <t>game-2</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="0" t="inlineStr">
         <is>
           <t>Brad Plays</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="0" t="inlineStr">
         <is>
           <t>brad</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="0" t="inlineStr">
         <is>
           <t>Brad</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="0" t="inlineStr">
         <is>
           <t>Team B</t>
         </is>
@@ -11598,34 +11664,34 @@
       <c r="H37" s="23" t="inlineStr"/>
       <c r="I37" s="23" t="inlineStr"/>
       <c r="J37" s="23" t="inlineStr"/>
-      <c r="K37">
+      <c r="K37" s="0">
         <f>IF(F37,SUM(G37:I37),"")</f>
         <v/>
       </c>
-      <c r="L37" t="inlineStr"/>
+      <c r="L37" s="0" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="0" t="inlineStr">
         <is>
           <t>game-2</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="0" t="inlineStr">
         <is>
           <t>Brad Plays</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="0" t="inlineStr">
         <is>
           <t>james</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="0" t="inlineStr">
         <is>
           <t>James</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="0" t="inlineStr">
         <is>
           <t>Team B</t>
         </is>
@@ -11637,34 +11703,34 @@
       <c r="H38" s="23" t="inlineStr"/>
       <c r="I38" s="23" t="inlineStr"/>
       <c r="J38" s="23" t="inlineStr"/>
-      <c r="K38">
+      <c r="K38" s="0">
         <f>IF(F38,SUM(G38:I38),"")</f>
         <v/>
       </c>
-      <c r="L38" t="inlineStr"/>
+      <c r="L38" s="0" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="0" t="inlineStr">
         <is>
           <t>game-2</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="0" t="inlineStr">
         <is>
           <t>Brad Plays</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="0" t="inlineStr">
         <is>
           <t>emil</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="0" t="inlineStr">
         <is>
           <t>Emil</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="0" t="inlineStr">
         <is>
           <t>Team C</t>
         </is>
@@ -11676,34 +11742,34 @@
       <c r="H39" s="23" t="inlineStr"/>
       <c r="I39" s="23" t="inlineStr"/>
       <c r="J39" s="23" t="inlineStr"/>
-      <c r="K39">
+      <c r="K39" s="0">
         <f>IF(F39,SUM(G39:I39),"")</f>
         <v/>
       </c>
-      <c r="L39" t="inlineStr"/>
+      <c r="L39" s="0" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="0" t="inlineStr">
         <is>
           <t>game-2</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="0" t="inlineStr">
         <is>
           <t>Brad Plays</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="0" t="inlineStr">
         <is>
           <t>darryl</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="0" t="inlineStr">
         <is>
           <t>Darryl</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="0" t="inlineStr">
         <is>
           <t>Team C</t>
         </is>
@@ -11715,34 +11781,34 @@
       <c r="H40" s="23" t="inlineStr"/>
       <c r="I40" s="23" t="inlineStr"/>
       <c r="J40" s="23" t="inlineStr"/>
-      <c r="K40">
+      <c r="K40" s="0">
         <f>IF(F40,SUM(G40:I40),"")</f>
         <v/>
       </c>
-      <c r="L40" t="inlineStr"/>
+      <c r="L40" s="0" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="0" t="inlineStr">
         <is>
           <t>game-2</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="0" t="inlineStr">
         <is>
           <t>Brad Plays</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="0" t="inlineStr">
         <is>
           <t>alan</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="0" t="inlineStr">
         <is>
           <t>Alan</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="0" t="inlineStr">
         <is>
           <t>Team C</t>
         </is>
@@ -11754,34 +11820,34 @@
       <c r="H41" s="23" t="inlineStr"/>
       <c r="I41" s="23" t="inlineStr"/>
       <c r="J41" s="23" t="inlineStr"/>
-      <c r="K41">
+      <c r="K41" s="0">
         <f>IF(F41,SUM(G41:I41),"")</f>
         <v/>
       </c>
-      <c r="L41" t="inlineStr"/>
+      <c r="L41" s="0" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="0" t="inlineStr">
         <is>
           <t>game-2</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="0" t="inlineStr">
         <is>
           <t>Brad Plays</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="0" t="inlineStr">
         <is>
           <t>andrew</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="0" t="inlineStr">
         <is>
           <t>Andrew</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="0" t="inlineStr">
         <is>
           <t>Team C</t>
         </is>
@@ -11793,34 +11859,34 @@
       <c r="H42" s="23" t="inlineStr"/>
       <c r="I42" s="23" t="inlineStr"/>
       <c r="J42" s="23" t="inlineStr"/>
-      <c r="K42">
+      <c r="K42" s="0">
         <f>IF(F42,SUM(G42:I42),"")</f>
         <v/>
       </c>
-      <c r="L42" t="inlineStr"/>
+      <c r="L42" s="0" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="0" t="inlineStr">
         <is>
           <t>game-3</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="0" t="inlineStr">
         <is>
           <t>Brad Plays</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="0" t="inlineStr">
         <is>
           <t>alex</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="0" t="inlineStr">
         <is>
           <t>Alex</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="0" t="inlineStr">
         <is>
           <t>Team A</t>
         </is>
@@ -11832,34 +11898,34 @@
       <c r="H43" s="23" t="inlineStr"/>
       <c r="I43" s="23" t="inlineStr"/>
       <c r="J43" s="23" t="inlineStr"/>
-      <c r="K43">
+      <c r="K43" s="0">
         <f>IF(F43,SUM(G43:I43),"")</f>
         <v/>
       </c>
-      <c r="L43" t="inlineStr"/>
+      <c r="L43" s="0" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="0" t="inlineStr">
         <is>
           <t>game-3</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="0" t="inlineStr">
         <is>
           <t>Brad Plays</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="0" t="inlineStr">
         <is>
           <t>peter</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="0" t="inlineStr">
         <is>
           <t>Peter</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="0" t="inlineStr">
         <is>
           <t>Team A</t>
         </is>
@@ -11871,34 +11937,34 @@
       <c r="H44" s="23" t="inlineStr"/>
       <c r="I44" s="23" t="inlineStr"/>
       <c r="J44" s="23" t="inlineStr"/>
-      <c r="K44">
+      <c r="K44" s="0">
         <f>IF(F44,SUM(G44:I44),"")</f>
         <v/>
       </c>
-      <c r="L44" t="inlineStr"/>
+      <c r="L44" s="0" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="0" t="inlineStr">
         <is>
           <t>game-3</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="0" t="inlineStr">
         <is>
           <t>Brad Plays</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="0" t="inlineStr">
         <is>
           <t>josh</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="0" t="inlineStr">
         <is>
           <t>Josh</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="0" t="inlineStr">
         <is>
           <t>Team A</t>
         </is>
@@ -11910,34 +11976,34 @@
       <c r="H45" s="23" t="inlineStr"/>
       <c r="I45" s="23" t="inlineStr"/>
       <c r="J45" s="23" t="inlineStr"/>
-      <c r="K45">
+      <c r="K45" s="0">
         <f>IF(F45,SUM(G45:I45),"")</f>
         <v/>
       </c>
-      <c r="L45" t="inlineStr"/>
+      <c r="L45" s="0" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="0" t="inlineStr">
         <is>
           <t>game-3</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="0" t="inlineStr">
         <is>
           <t>Brad Plays</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="0" t="inlineStr">
         <is>
           <t>berler</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="0" t="inlineStr">
         <is>
           <t>Berler</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="0" t="inlineStr">
         <is>
           <t>Team A</t>
         </is>
@@ -11949,38 +12015,38 @@
       <c r="H46" s="23" t="inlineStr"/>
       <c r="I46" s="23" t="inlineStr"/>
       <c r="J46" s="23" t="inlineStr"/>
-      <c r="K46">
+      <c r="K46" s="0">
         <f>IF(F46,SUM(G46:I46),"")</f>
         <v/>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="L46" s="0" t="inlineStr">
         <is>
           <t>Shared sub slot</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="0" t="inlineStr">
         <is>
           <t>game-3</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="0" t="inlineStr">
         <is>
           <t>Brad Plays</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="0" t="inlineStr">
         <is>
           <t>jason</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="0" t="inlineStr">
         <is>
           <t>Jason</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="0" t="inlineStr">
         <is>
           <t>Team A</t>
         </is>
@@ -11992,38 +12058,38 @@
       <c r="H47" s="23" t="inlineStr"/>
       <c r="I47" s="23" t="inlineStr"/>
       <c r="J47" s="23" t="inlineStr"/>
-      <c r="K47">
+      <c r="K47" s="0">
         <f>IF(F47,SUM(G47:I47),"")</f>
         <v/>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="L47" s="0" t="inlineStr">
         <is>
           <t>Shared sub slot</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="0" t="inlineStr">
         <is>
           <t>game-3</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="0" t="inlineStr">
         <is>
           <t>Brad Plays</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="0" t="inlineStr">
         <is>
           <t>emil</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="0" t="inlineStr">
         <is>
           <t>Emil</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="0" t="inlineStr">
         <is>
           <t>Team C</t>
         </is>
@@ -12035,34 +12101,34 @@
       <c r="H48" s="23" t="inlineStr"/>
       <c r="I48" s="23" t="inlineStr"/>
       <c r="J48" s="23" t="inlineStr"/>
-      <c r="K48">
+      <c r="K48" s="0">
         <f>IF(F48,SUM(G48:I48),"")</f>
         <v/>
       </c>
-      <c r="L48" t="inlineStr"/>
+      <c r="L48" s="0" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="0" t="inlineStr">
         <is>
           <t>game-3</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="0" t="inlineStr">
         <is>
           <t>Brad Plays</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="0" t="inlineStr">
         <is>
           <t>darryl</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="0" t="inlineStr">
         <is>
           <t>Darryl</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="0" t="inlineStr">
         <is>
           <t>Team C</t>
         </is>
@@ -12074,34 +12140,34 @@
       <c r="H49" s="23" t="inlineStr"/>
       <c r="I49" s="23" t="inlineStr"/>
       <c r="J49" s="23" t="inlineStr"/>
-      <c r="K49">
+      <c r="K49" s="0">
         <f>IF(F49,SUM(G49:I49),"")</f>
         <v/>
       </c>
-      <c r="L49" t="inlineStr"/>
+      <c r="L49" s="0" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="0" t="inlineStr">
         <is>
           <t>game-3</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="0" t="inlineStr">
         <is>
           <t>Brad Plays</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="0" t="inlineStr">
         <is>
           <t>alan</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="0" t="inlineStr">
         <is>
           <t>Alan</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="0" t="inlineStr">
         <is>
           <t>Team C</t>
         </is>
@@ -12113,34 +12179,34 @@
       <c r="H50" s="23" t="inlineStr"/>
       <c r="I50" s="23" t="inlineStr"/>
       <c r="J50" s="23" t="inlineStr"/>
-      <c r="K50">
+      <c r="K50" s="0">
         <f>IF(F50,SUM(G50:I50),"")</f>
         <v/>
       </c>
-      <c r="L50" t="inlineStr"/>
+      <c r="L50" s="0" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="0" t="inlineStr">
         <is>
           <t>game-3</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="0" t="inlineStr">
         <is>
           <t>Brad Plays</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="0" t="inlineStr">
         <is>
           <t>andrew</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="0" t="inlineStr">
         <is>
           <t>Andrew</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="0" t="inlineStr">
         <is>
           <t>Team C</t>
         </is>
@@ -12152,11 +12218,11 @@
       <c r="H51" s="23" t="inlineStr"/>
       <c r="I51" s="23" t="inlineStr"/>
       <c r="J51" s="23" t="inlineStr"/>
-      <c r="K51">
+      <c r="K51" s="0">
         <f>IF(F51,SUM(G51:I51),"")</f>
         <v/>
       </c>
-      <c r="L51" t="inlineStr"/>
+      <c r="L51" s="0" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L1"/>

--- a/resources/bachelor_player_ratings_shared.xlsx
+++ b/resources/bachelor_player_ratings_shared.xlsx
@@ -16,6 +16,7 @@
     <sheet name="Bet Legs" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Betting Leaderboard" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Player Leaderboard" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Game Rosters" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'App Config'!$A$1:$D$1</definedName>
@@ -231,7 +232,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -297,6 +298,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2079,13 +2081,73 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" style="19" min="1" max="1"/>
+    <col width="22" customWidth="1" style="19" min="2" max="2"/>
+    <col width="13" customWidth="1" style="19" min="3" max="3"/>
+    <col width="22" customWidth="1" style="19" min="4" max="4"/>
+    <col width="16" customWidth="1" style="19" min="5" max="5"/>
+    <col width="11" customWidth="1" style="19" min="6" max="6"/>
+    <col width="42" customWidth="1" style="19" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>Game ID</t>
+        </is>
+      </c>
+      <c r="B1" s="31" t="inlineStr">
+        <is>
+          <t>Roster Configuration</t>
+        </is>
+      </c>
+      <c r="C1" s="31" t="inlineStr">
+        <is>
+          <t>Team ID</t>
+        </is>
+      </c>
+      <c r="D1" s="31" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="E1" s="31" t="inlineStr">
+        <is>
+          <t>Rotation Share</t>
+        </is>
+      </c>
+      <c r="F1" s="31" t="inlineStr">
+        <is>
+          <t>Active?</t>
+        </is>
+      </c>
+      <c r="G1" s="31" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" style="19" min="1" max="1"/>
@@ -2317,6 +2379,226 @@
         </is>
       </c>
       <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>Organizer</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>STRAIGHT_VIG</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Straight-market overround used for game lines and player props.</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>Organizer</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t>PARLAY_BASE_VIG</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Base parlay margin applied after joint simulation pricing.</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>Organizer</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>REBOUND_LINE_QUANTILE</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Conservative rebound line percentile.</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>Organizer</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>ASSIST_LINE_QUANTILE</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Conservative assist line percentile.</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Organizer</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t>THREES_LINE_QUANTILE</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Conservative made-three line percentile.</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>Organizer</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t>COMBO_LINE_QUANTILE</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Conservative combo-prop line percentile.</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>Organizer</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t>THREE_POINT_RATE_MIN</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Minimum amateur pickup three-point attempt rate.</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>Organizer</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t>THREE_POINT_RATE_MAX</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Maximum amateur pickup three-point attempt rate.</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>Organizer</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t>ASSIST_BASE_RATE</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Base chance that a made basket receives an assist.</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>Organizer</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>ASSIST_PLAYMAKING_SLOPE</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Assist-rate increase per playmaking rating point.</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Organizer</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t>OFFENSIVE_REBOUND_BASE_RATE</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t>Base chance a miss becomes an offensive rebound.</t>
+        </is>
+      </c>
+      <c r="D22" s="0" t="inlineStr">
         <is>
           <t>Organizer</t>
         </is>
@@ -9915,7 +10197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="19" min="1" max="1"/>
@@ -10005,6 +10287,36 @@
           <t>Reconciliation</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Game Type</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Team 1 ID</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Team 2 ID</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Bye ID</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Counts Toward Standings?</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Betting Enabled?</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -10056,6 +10368,26 @@
         <f>IF(NOT($I2),"PENDING",IF(AND($G2=$L2,$H2=$M2),"OK","CHECK PLAYER POINTS"))</f>
         <v/>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>TOURNAMENT</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Team A</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Team B</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Team C</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
@@ -10107,6 +10439,26 @@
         <f>IF(NOT($I3),"PENDING",IF(AND($G3=$L3,$H3=$M3),"OK","CHECK PLAYER POINTS"))</f>
         <v/>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>TOURNAMENT</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Team B</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Team C</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Team A</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
@@ -10157,6 +10509,26 @@
       <c r="N4" s="30">
         <f>IF(NOT($I4),"PENDING",IF(AND($G4=$L4,$H4=$M4),"OK","CHECK PLAYER POINTS"))</f>
         <v/>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>TOURNAMENT</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Team C</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Team A</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Team B</t>
+        </is>
       </c>
     </row>
   </sheetData>
